--- a/CoDPSO_Results_D10.xlsx
+++ b/CoDPSO_Results_D10.xlsx
@@ -617,22 +617,22 @@
         <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>345.181845833064</v>
+        <v>341.2767252782094</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>30.29306902623741</v>
+        <v>24.26519444520479</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>306.1476926699696</v>
+        <v>301.9143542803455</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>411.0842677640592</v>
+        <v>395.9127863568975</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>45.18184583306396</v>
+        <v>41.27672527820937</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>30.29306902623741</v>
+        <v>24.26519444520479</v>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
@@ -654,22 +654,22 @@
         <v>1.95</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>408.4648190028985</v>
+        <v>409.0570042477048</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>5.114745059415579</v>
+        <v>5.782418012014913</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>400.7968474534707</v>
+        <v>401.5352477151633</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>424.3937663438297</v>
+        <v>430.018465005009</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>7.684819002898564</v>
+        <v>8.277004247704781</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>3.164745059415579</v>
+        <v>3.832418012014913</v>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
@@ -691,22 +691,22 @@
         <v>0.00898</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>600.0004570904993</v>
+        <v>600.0005312746379</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.0002876415047275072</v>
+        <v>0.0002265240092068909</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>600.000120201376</v>
+        <v>600.0001507317784</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>600.001207269429</v>
+        <v>600.0010791176591</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.0004570904992533542</v>
+        <v>0.0005312746378649535</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.008692358495272492</v>
+        <v>-0.008753475990793109</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -728,22 +728,22 @@
         <v>2.67</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>831.9067013214733</v>
+        <v>831.0972777942225</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>8.543666086518538</v>
+        <v>11.2789593674607</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>814.1295186661062</v>
+        <v>816.0001941859394</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>852.1923257442302</v>
+        <v>852.0000007805262</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>25.07670132147325</v>
+        <v>24.26727779422242</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>5.873666086518538</v>
+        <v>8.608959367460701</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
         <v>0.0413</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>900.1261108857981</v>
+        <v>900.1481647637037</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1220116415699311</v>
+        <v>0.1388866884074056</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>900.0010050738578</v>
+        <v>900.0040942381161</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>900.5503285757802</v>
+        <v>900.5494548576048</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.1161108857980935</v>
+        <v>0.1381647637036849</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.08071164156993112</v>
+        <v>0.09758668840740564</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -802,22 +802,22 @@
         <v>59.1</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>16395.9759788934</v>
+        <v>17481.39541177408</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>5401.716371880299</v>
+        <v>6048.262535437532</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>8026.248019343919</v>
+        <v>5025.937928620318</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>27430.13192133232</v>
+        <v>29691.02286936876</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>14524.1159788934</v>
+        <v>15609.53541177408</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5342.616371880299</v>
+        <v>5989.162535437532</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -839,22 +839,22 @@
         <v>9.66</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2041.08111176205</v>
+        <v>2040.475195562317</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8.67636700441915</v>
+        <v>8.124199473454231</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2030.284147056672</v>
+        <v>2021.013690010596</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2067.898854828567</v>
+        <v>2061.463757656976</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>31.73111176205043</v>
+        <v>31.12519556231723</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.9836329955808498</v>
+        <v>-1.535800526545769</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -876,22 +876,22 @@
         <v>10</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2252.152061477382</v>
+        <v>2260.669409745225</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>22.04641774298475</v>
+        <v>49.3529727926692</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2225.812189027058</v>
+        <v>2227.597503796951</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2306.559774649785</v>
+        <v>2500.679190173065</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>42.09206147738223</v>
+        <v>50.60940974522509</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>12.04641774298475</v>
+        <v>39.3529727926692</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -913,22 +913,22 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2466.994728515501</v>
+        <v>2482.559203627215</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>176.1999832259334</v>
+        <v>174.95896824201</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2304.658901879289</v>
+        <v>2304.368804120033</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2736.450985556699</v>
+        <v>2736.444970119394</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>-62.28527148449894</v>
+        <v>-46.72079637278557</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>176.1999832259334</v>
+        <v>174.95896824201</v>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
@@ -950,22 +950,22 @@
         <v>0.518</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2628.099555650998</v>
+        <v>2632.894283480912</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.082246430819266</v>
+        <v>22.30649103243176</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2622.896698373681</v>
+        <v>2623.414907756083</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2641.273796909476</v>
+        <v>2751.466995099225</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>127.459555650998</v>
+        <v>132.2542834809124</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>3.564246430819266</v>
+        <v>21.78849103243176</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
         <v>54.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2604.981720840861</v>
+        <v>2606.053673131233</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.975927508039526</v>
+        <v>5.777740123804923</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2600.848361263776</v>
+        <v>2601.319994148277</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2620.493057678433</v>
+        <v>2622.66273382562</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>-5.018279159138729</v>
+        <v>-3.946326868767301</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-49.82407249196047</v>
+        <v>-49.02225987619507</v>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
@@ -1024,22 +1024,22 @@
         <v>0.946</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2867.159387166466</v>
+        <v>2869.939433637538</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>17.79378470288678</v>
+        <v>1.764276732667429</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2771.900797700995</v>
+        <v>2868.184325389537</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2875.966828463754</v>
+        <v>2875.617276819583</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>5.549387166466204</v>
+        <v>8.329433637537932</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>16.84778470288677</v>
+        <v>0.8182767326674287</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -1901,94 +1901,94 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>313.4126559636028</v>
+        <v>321.9124517871341</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>337.2909840939007</v>
+        <v>314.0707706730805</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>375.4442361283058</v>
+        <v>350.0046465464358</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>379.9446665079954</v>
+        <v>387.6400744134166</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>390.2193838521342</v>
+        <v>349.4792534340656</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>384.0810558967423</v>
+        <v>377.357365048929</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>331.7103012488654</v>
+        <v>335.492709703153</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>335.3377165432498</v>
+        <v>356.5127508918586</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>346.6656496303086</v>
+        <v>359.9154739430958</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>319.0765076863389</v>
+        <v>395.9127863568975</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>405.2236218930587</v>
+        <v>306.4037853189984</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>323.2037253741299</v>
+        <v>334.5964368811302</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>325.4441639346269</v>
+        <v>365.7323947964663</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>311.0887874237838</v>
+        <v>310.7393124716679</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>336.4232640528134</v>
+        <v>327.8594050707321</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>325.2696189508326</v>
+        <v>328.2871226103289</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>408.3534969285226</v>
+        <v>321.8613859955478</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>370.7521070600787</v>
+        <v>301.9143542803455</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>329.8648090784183</v>
+        <v>378.80270963656</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>341.4179398120684</v>
+        <v>361.3371552250873</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>313.1024958775163</v>
+        <v>339.7957685245354</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>340.4186124163563</v>
+        <v>346.1438792299954</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>334.6408262866108</v>
+        <v>334.1105529094777</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>306.1476926699696</v>
+        <v>325.7085015390989</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>320.1490701219569</v>
+        <v>341.8135047662314</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>337.9709514515097</v>
+        <v>325.5062287793513</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>353.5065626131245</v>
+        <v>334.1674940176969</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>411.0842677640592</v>
+        <v>305.3264138781733</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>332.9976239841735</v>
+        <v>335.5112668655145</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>315.2125797468669</v>
+        <v>364.3858027512757</v>
       </c>
       <c r="AF3" s="14">
         <f>AVERAGE(B3:AE3)</f>
@@ -2014,94 +2014,94 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>424.3937663438297</v>
+        <v>403.1020682528393</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>402.8457604779274</v>
+        <v>403.4935190084236</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>404.1788813231053</v>
+        <v>404.3846572609367</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>410.7874202072824</v>
+        <v>411.0016587795204</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>405.3752642601632</v>
+        <v>408.9793218372212</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>403.2455908741349</v>
+        <v>408.4232321419059</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>408.3233374841845</v>
+        <v>408.428281558807</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>409.40643487083</v>
+        <v>404.2699469317884</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>409.5046056397618</v>
+        <v>408.5305076320592</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>403.5166351945191</v>
+        <v>412.0643131244716</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>409.4112171563142</v>
+        <v>412.7342574897095</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>408.1346291148105</v>
+        <v>404.3749917848873</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>409.9382673569907</v>
+        <v>411.279611662619</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>419.4795139742663</v>
+        <v>401.5352477151633</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>406.5194891224456</v>
+        <v>410.8458255261779</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>405.9934006984309</v>
+        <v>403.9600059869433</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>400.7968474534707</v>
+        <v>420.2550846258457</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>408.345015510872</v>
+        <v>402.2936990990556</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>405.2891547137615</v>
+        <v>409.7057290122679</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>408.3236229655973</v>
+        <v>417.2920028116228</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>407.8264006010087</v>
+        <v>406.3927719348927</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>420.2031715340316</v>
+        <v>412.198280839651</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>405.544899425205</v>
+        <v>408.3116853445874</v>
       </c>
       <c r="Y4" s="8" t="n">
-        <v>409.2355261958505</v>
+        <v>407.563077246152</v>
       </c>
       <c r="Z4" s="8" t="n">
-        <v>409.4245737510728</v>
+        <v>411.2149046119302</v>
       </c>
       <c r="AA4" s="8" t="n">
-        <v>411.2195480676954</v>
+        <v>408.2752948529218</v>
       </c>
       <c r="AB4" s="8" t="n">
-        <v>409.0779145417025</v>
+        <v>407.8748188845341</v>
       </c>
       <c r="AC4" s="8" t="n">
-        <v>410.2424292599096</v>
+        <v>410.5247655293452</v>
       </c>
       <c r="AD4" s="8" t="n">
-        <v>405.1026502204277</v>
+        <v>402.3821009398529</v>
       </c>
       <c r="AE4" s="8" t="n">
-        <v>402.2586017473569</v>
+        <v>430.018465005009</v>
       </c>
       <c r="AF4" s="14">
         <f>AVERAGE(B4:AE4)</f>
@@ -2127,94 +2127,94 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>600.0002273891405</v>
+        <v>600.000694450291</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>600.0002736671415</v>
+        <v>600.0001531142539</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>600.0007238576698</v>
+        <v>600.0008690321421</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>600.0001919568209</v>
+        <v>600.0004471279427</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>600.000708553602</v>
+        <v>600.0006846658384</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>600.000743723118</v>
+        <v>600.0010791176591</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>600.0005779759616</v>
+        <v>600.0001943147299</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>600.0001799146617</v>
+        <v>600.0005062337818</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>600.0004031304838</v>
+        <v>600.0001507317784</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>600.0005477299048</v>
+        <v>600.0005434748451</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>600.0011179132409</v>
+        <v>600.0004629770082</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>600.0003959326563</v>
+        <v>600.000169718492</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>600.0005704353255</v>
+        <v>600.000444947748</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>600.0003962533476</v>
+        <v>600.0005040808539</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>600.0003034464156</v>
+        <v>600.0007384728082</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>600.000120201376</v>
+        <v>600.000275426056</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>600.0001213282396</v>
+        <v>600.0006960794104</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>600.00032069113</v>
+        <v>600.0006191650599</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>600.001207269429</v>
+        <v>600.0005311717495</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>600.0002547921056</v>
+        <v>600.0007405632351</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>600.0002993350519</v>
+        <v>600.0004115172968</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>600.0001463883023</v>
+        <v>600.0004369921165</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>600.0009732247598</v>
+        <v>600.0003061778413</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>600.0002423185354</v>
+        <v>600.0006594507098</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>600.0002349870488</v>
+        <v>600.0004385795211</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>600.0008253288937</v>
+        <v>600.0006465219577</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>600.0003286806904</v>
+        <v>600.0005239484223</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>600.0003071832139</v>
+        <v>600.0005656669412</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>600.0003900830684</v>
+        <v>600.0009949900953</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>600.0005790236473</v>
+        <v>600.0004495285518</v>
       </c>
       <c r="AF5" s="14">
         <f>AVERAGE(B5:AE5)</f>
@@ -2240,94 +2240,94 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>836.0021483789112</v>
+        <v>822.0016219140912</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>833.0302199587759</v>
+        <v>818.0000015561309</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>830.0014026021304</v>
+        <v>824.0005695965789</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>822.2652551014608</v>
+        <v>820.015101789144</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>828.0001066994865</v>
+        <v>830.0000013438486</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>822.0029426701964</v>
+        <v>818.0000002894594</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>824.0467211189184</v>
+        <v>828.0021762243275</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>830.0217078200501</v>
+        <v>816.0415363262896</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>825.3411142320588</v>
+        <v>830.008141243644</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>826.0166750558752</v>
+        <v>850.0000014890418</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>818.0062023269475</v>
+        <v>828.0012179909211</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>842.0000012096277</v>
+        <v>834.0000371136103</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>828.0000078975903</v>
+        <v>824.048127898555</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>838.0000246772718</v>
+        <v>830.0610070319133</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>834.0000417862917</v>
+        <v>832.0003021843006</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>838.000147364875</v>
+        <v>820.1633055402108</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>844.0003479411943</v>
+        <v>842.0401415776919</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>814.1295186661062</v>
+        <v>846.0000000140686</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>828.0004657437663</v>
+        <v>830.9770806355097</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>852.1923257442302</v>
+        <v>819.6910400244891</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>834.0020267099786</v>
+        <v>852.000000424985</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>830.0000000022815</v>
+        <v>828.4130799487483</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>840.0000000135816</v>
+        <v>816.0001941859394</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>832.1373333874581</v>
+        <v>832.0061586138727</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>830.0000006824802</v>
+        <v>844.0184232078475</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>818.0002704727765</v>
+        <v>850.0000541855777</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>838.0002235043919</v>
+        <v>852.0000007805262</v>
       </c>
       <c r="AC6" s="8" t="n">
-        <v>842.0000001489008</v>
+        <v>821.3407927035115</v>
       </c>
       <c r="AD6" s="8" t="n">
-        <v>840.0029701603926</v>
+        <v>828.0882179918352</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>840.0008375661903</v>
+        <v>846.0000000000058</v>
       </c>
       <c r="AF6" s="14">
         <f>AVERAGE(B6:AE6)</f>
@@ -2353,94 +2353,94 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>900.1916847082483</v>
+        <v>900.2119505884526</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>900.0969001257412</v>
+        <v>900.1587795703563</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>900.1825591087454</v>
+        <v>900.0137780937523</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>900.1164078732747</v>
+        <v>900.493637923997</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>900.1027371814454</v>
+        <v>900.0704908080892</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>900.1394674776589</v>
+        <v>900.2844683377039</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>900.0944757633981</v>
+        <v>900.2075477895318</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>900.2745462573658</v>
+        <v>900.0928669627586</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>900.0051467051944</v>
+        <v>900.0226336782196</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>900.0275231315167</v>
+        <v>900.0140605986109</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>900.099825855645</v>
+        <v>900.1111722845966</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>900.0913153154254</v>
+        <v>900.1027580705271</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>900.011300626036</v>
+        <v>900.0085653124434</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>900.185212340993</v>
+        <v>900.5494548576048</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>900.0152885214983</v>
+        <v>900.010479045329</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>900.4265293827985</v>
+        <v>900.0462144792057</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>900.0149480471133</v>
+        <v>900.2233463542666</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>900.218883963784</v>
+        <v>900.1350553521734</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>900.1810117836706</v>
+        <v>900.0343474543939</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>900.0182604812841</v>
+        <v>900.0040942381161</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>900.1954392487061</v>
+        <v>900.1864908091544</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>900.1303992339252</v>
+        <v>900.0195301761563</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>900.0700510429348</v>
+        <v>900.161829560605</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>900.5503285757802</v>
+        <v>900.4327683389189</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>900.0098240967367</v>
+        <v>900.1857645542412</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>900.1597430123992</v>
+        <v>900.1235467522696</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>900.0825812377839</v>
+        <v>900.1015054269752</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>900.0497014634282</v>
+        <v>900.0438645444419</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>900.0402289375528</v>
+        <v>900.1852354494749</v>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>900.0010050738578</v>
+        <v>900.2087054987505</v>
       </c>
       <c r="AF7" s="14">
         <f>AVERAGE(B7:AE7)</f>
@@ -2466,94 +2466,94 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>16268.33053928933</v>
+        <v>20641.59216537873</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>25216.14537628783</v>
+        <v>22578.49338522329</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>13479.98989140366</v>
+        <v>10862.20832302194</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>19079.75090996408</v>
+        <v>18168.30260875679</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>17010.663824534</v>
+        <v>16232.84726293689</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>13947.42841285069</v>
+        <v>9411.654045410703</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>18632.3980160672</v>
+        <v>17003.3321624544</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>11157.94615056496</v>
+        <v>5025.937928620318</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>23275.70073267048</v>
+        <v>20641.18429682944</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>10177.22205918188</v>
+        <v>15637.68643934662</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>16626.37245660527</v>
+        <v>19760.89149975024</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>10384.61547152551</v>
+        <v>12342.70237424351</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>16025.81276136762</v>
+        <v>23903.0801485195</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>9332.769157526162</v>
+        <v>20799.33293960076</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>15100.08453336068</v>
+        <v>17085.46576967182</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>23113.23941599866</v>
+        <v>20383.0840708264</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>18435.96856835578</v>
+        <v>13078.04438130791</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>11344.31214572256</v>
+        <v>8144.488528078272</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>8026.248019343919</v>
+        <v>12672.27608863283</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>24226.62198342237</v>
+        <v>8750.981268674008</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>17711.37984775598</v>
+        <v>28503.55649558385</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>10773.69862069204</v>
+        <v>17554.05617494225</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>14829.08174701569</v>
+        <v>28131.29917345991</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>17323.48032025368</v>
+        <v>17763.75503129092</v>
       </c>
       <c r="Z8" s="8" t="n">
-        <v>21227.24305089428</v>
+        <v>9465.404666185932</v>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>10244.78966460783</v>
+        <v>21286.50622260097</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>11846.99284504811</v>
+        <v>21230.13928527885</v>
       </c>
       <c r="AC8" s="8" t="n">
-        <v>27430.13192133232</v>
+        <v>20037.61224116832</v>
       </c>
       <c r="AD8" s="8" t="n">
-        <v>12769.51576232177</v>
+        <v>29691.02286936876</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>26861.34516083766</v>
+        <v>17654.92450605825</v>
       </c>
       <c r="AF8" s="14">
         <f>AVERAGE(B8:AE8)</f>
@@ -2579,94 +2579,94 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2039.796543040454</v>
+        <v>2044.455452800737</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2057.311142102101</v>
+        <v>2056.106296537024</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2044.542439550895</v>
+        <v>2038.035013907244</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2040.260366907062</v>
+        <v>2040.472808779659</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2042.420652649301</v>
+        <v>2043.853492872288</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2031.84612595214</v>
+        <v>2037.171005495361</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2035.401322136589</v>
+        <v>2048.757664399437</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2041.127256799809</v>
+        <v>2030.644569298526</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2041.774464209781</v>
+        <v>2040.42400891951</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2033.151680772403</v>
+        <v>2034.674710421522</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2035.741163662973</v>
+        <v>2042.219449894825</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2030.284147056672</v>
+        <v>2044.141362350047</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2031.402346577123</v>
+        <v>2034.55375258638</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2033.527280232716</v>
+        <v>2044.676517661042</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2057.87642303598</v>
+        <v>2038.143388566359</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2038.636586214921</v>
+        <v>2039.723696986222</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2067.898854828567</v>
+        <v>2031.939891828064</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>2039.406363830633</v>
+        <v>2031.274257299484</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>2041.419015017558</v>
+        <v>2035.621612912873</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2043.499930854079</v>
+        <v>2051.598816910738</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2038.876685343622</v>
+        <v>2044.004459812047</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2036.449430515962</v>
+        <v>2040.207807908164</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2044.031071780615</v>
+        <v>2040.332267915169</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2040.201078909248</v>
+        <v>2039.399041097204</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2046.736897947892</v>
+        <v>2021.013690010596</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>2035.611792368832</v>
+        <v>2033.525804087</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>2036.665593675042</v>
+        <v>2061.463757656976</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>2057.784599238475</v>
+        <v>2035.311821958664</v>
       </c>
       <c r="AD9" s="4" t="n">
-        <v>2034.316021358227</v>
+        <v>2036.335298467357</v>
       </c>
       <c r="AE9" s="4" t="n">
-        <v>2034.436076291836</v>
+        <v>2054.174147529007</v>
       </c>
       <c r="AF9" s="14">
         <f>AVERAGE(B9:AE9)</f>
@@ -2692,94 +2692,94 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>2296.831823819285</v>
+        <v>2245.290346552693</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2228.653519127779</v>
+        <v>2237.39428418271</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2233.470792139764</v>
+        <v>2276.552244503348</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>2261.892894165339</v>
+        <v>2244.247178077148</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2288.314701530491</v>
+        <v>2271.937376079521</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2236.602582084723</v>
+        <v>2229.800575824169</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>2249.167777132918</v>
+        <v>2236.314067256545</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>2246.058131939818</v>
+        <v>2244.485689705265</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>2241.12311673884</v>
+        <v>2227.597503796951</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>2275.996875803763</v>
+        <v>2270.803184844114</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>2227.807651890201</v>
+        <v>2242.365362463114</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>2244.835697988624</v>
+        <v>2228.984267355373</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>2231.116579713675</v>
+        <v>2242.144302970354</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>2272.957546394179</v>
+        <v>2231.825393349728</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>2251.345433302181</v>
+        <v>2302.461712666685</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>2255.018507991444</v>
+        <v>2258.18810197484</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>2229.395710573367</v>
+        <v>2258.764591552238</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>2253.96733092631</v>
+        <v>2234.203262914444</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>2271.217990800953</v>
+        <v>2282.421151575762</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>2225.812189027058</v>
+        <v>2261.891643996481</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>2243.066674513555</v>
+        <v>2237.655354644296</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>2244.896291333282</v>
+        <v>2241.10976669832</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>2229.321728516614</v>
+        <v>2243.2315484926</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>2287.297874008424</v>
+        <v>2239.346817170516</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>2253.332562254332</v>
+        <v>2500.679190173065</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>2271.081698034374</v>
+        <v>2315.762208817869</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>2234.1927025692</v>
+        <v>2238.562241243082</v>
       </c>
       <c r="AC10" s="8" t="n">
-        <v>2246.029071710127</v>
+        <v>2271.528821549473</v>
       </c>
       <c r="AD10" s="8" t="n">
-        <v>2227.196613641058</v>
+        <v>2260.499548553656</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>2306.559774649785</v>
+        <v>2244.034553372376</v>
       </c>
       <c r="AF10" s="14">
         <f>AVERAGE(B10:AE10)</f>
@@ -2805,94 +2805,94 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2307.970323748879</v>
+        <v>2356.839794868658</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2304.658901879289</v>
+        <v>2736.444970119394</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2317.640603119663</v>
+        <v>2670.136108532151</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2666.227032619909</v>
+        <v>2318.290410915088</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2681.248087389461</v>
+        <v>2675.26743251075</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2317.522384712739</v>
+        <v>2309.003033828419</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2305.596723737396</v>
+        <v>2670.672230181071</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2688.434788686639</v>
+        <v>2366.556335944204</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2306.886053720522</v>
+        <v>2310.184435241171</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2417.51383505581</v>
+        <v>2667.000015288601</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2327.53798597369</v>
+        <v>2667.958764001588</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2307.866544177414</v>
+        <v>2668.868952503279</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2670.114908970314</v>
+        <v>2676.338006307773</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2670.123780057892</v>
+        <v>2680.251216736825</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2736.450985556699</v>
+        <v>2312.574703193933</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2309.188338911556</v>
+        <v>2307.277266833745</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2429.808304620981</v>
+        <v>2328.079020666872</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2698.258075182658</v>
+        <v>2307.878952581268</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2669.497151731088</v>
+        <v>2667.372549255771</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2312.42045910354</v>
+        <v>2305.953281398236</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2670.457503992894</v>
+        <v>2320.601204773012</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2671.355903120289</v>
+        <v>2670.121343943819</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2319.020094397453</v>
+        <v>2313.341767635307</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>2311.416876228996</v>
+        <v>2675.656567617533</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2666.438261448316</v>
+        <v>2309.421687799866</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>2666.968441358091</v>
+        <v>2308.895088722029</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>2313.639445728068</v>
+        <v>2680.271324810987</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>2313.542427227111</v>
+        <v>2304.368804120033</v>
       </c>
       <c r="AD11" s="4" t="n">
-        <v>2309.304977702552</v>
+        <v>2516.113225118315</v>
       </c>
       <c r="AE11" s="4" t="n">
-        <v>2322.73265530514</v>
+        <v>2375.037613366744</v>
       </c>
       <c r="AF11" s="14">
         <f>AVERAGE(B11:AE11)</f>
@@ -2918,94 +2918,94 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>2625.261347093641</v>
+        <v>2624.112055992699</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>2627.86695856567</v>
+        <v>2630.103106368782</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2629.106050309121</v>
+        <v>2629.884121646029</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2623.828093835403</v>
+        <v>2628.155256210339</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2627.323990985604</v>
+        <v>2625.514147540115</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2625.455501749006</v>
+        <v>2627.91941492664</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>2638.219168555771</v>
+        <v>2625.941452122996</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>2629.124851830721</v>
+        <v>2625.316417320637</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>2634.096194946253</v>
+        <v>2633.918827405399</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>2630.378378417785</v>
+        <v>2630.707881185127</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>2625.874651843029</v>
+        <v>2628.612866757715</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>2629.012467165496</v>
+        <v>2634.443459010084</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>2626.95166048386</v>
+        <v>2636.872104968443</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>2627.082309108338</v>
+        <v>2635.935133002065</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>2641.273796909476</v>
+        <v>2628.903410288913</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>2630.404205777301</v>
+        <v>2635.082854883137</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>2626.783975835913</v>
+        <v>2623.414907756083</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>2625.120874544958</v>
+        <v>2628.870877428848</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>2622.896698373681</v>
+        <v>2631.747948591898</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>2627.553658427985</v>
+        <v>2626.412942086477</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>2623.775517655236</v>
+        <v>2629.681435653506</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>2631.03886237554</v>
+        <v>2627.949111180134</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>2627.977514314204</v>
+        <v>2624.798708861438</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>2624.661944933821</v>
+        <v>2630.277897383314</v>
       </c>
       <c r="Z12" s="8" t="n">
-        <v>2628.410024301835</v>
+        <v>2623.779567792526</v>
       </c>
       <c r="AA12" s="8" t="n">
-        <v>2625.350468223297</v>
+        <v>2626.605150267518</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>2631.811693382484</v>
+        <v>2751.466995099225</v>
       </c>
       <c r="AC12" s="8" t="n">
-        <v>2624.112392797371</v>
+        <v>2628.30622102076</v>
       </c>
       <c r="AD12" s="8" t="n">
-        <v>2623.768473925461</v>
+        <v>2626.324294325309</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>2628.464942861681</v>
+        <v>2625.769937351196</v>
       </c>
       <c r="AF12" s="14">
         <f>AVERAGE(B12:AE12)</f>
@@ -3031,94 +3031,94 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2602.249321124202</v>
+        <v>2601.566296411168</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2604.445034705159</v>
+        <v>2604.225326361059</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2614.705802639155</v>
+        <v>2602.157395048499</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2601.745711885512</v>
+        <v>2602.634505984717</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2601.076751464785</v>
+        <v>2616.492279450525</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2602.037519128939</v>
+        <v>2602.919870502931</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2610.711663303381</v>
+        <v>2603.469473132985</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2602.530855609831</v>
+        <v>2618.033208566118</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2614.409032411437</v>
+        <v>2602.43866456828</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2602.726097979619</v>
+        <v>2605.879094134668</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2605.274670352124</v>
+        <v>2610.606772880424</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2602.224489814179</v>
+        <v>2602.320763314845</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2601.522804819048</v>
+        <v>2602.938688156172</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2620.493057678433</v>
+        <v>2606.842049761417</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2602.807741282392</v>
+        <v>2603.964216140795</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2600.848361263776</v>
+        <v>2601.464571282288</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>2602.912590432861</v>
+        <v>2604.47396301658</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>2602.691681039007</v>
+        <v>2603.814982526348</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>2602.601554978679</v>
+        <v>2604.215190851144</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2601.41774371885</v>
+        <v>2622.66273382562</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2601.522329936112</v>
+        <v>2601.319994148277</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2610.522222131265</v>
+        <v>2605.890774758822</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2601.143772229385</v>
+        <v>2602.390553721258</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2607.493630436081</v>
+        <v>2604.610115345456</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2602.399662273736</v>
+        <v>2601.401367629295</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>2603.039690172682</v>
+        <v>2605.260168418212</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>2601.568515796293</v>
+        <v>2619.653576914802</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>2601.534894255147</v>
+        <v>2601.728297630881</v>
       </c>
       <c r="AD13" s="4" t="n">
-        <v>2612.269153797604</v>
+        <v>2603.674353305375</v>
       </c>
       <c r="AE13" s="4" t="n">
-        <v>2608.525268566165</v>
+        <v>2612.56094614802</v>
       </c>
       <c r="AF13" s="14">
         <f>AVERAGE(B13:AE13)</f>
@@ -3144,94 +3144,94 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>2871.352385563575</v>
+        <v>2873.675668038233</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2868.37456159339</v>
+        <v>2871.49425486583</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2868.964510041559</v>
+        <v>2870.730595407148</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>2869.176134408261</v>
+        <v>2869.037937017383</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2868.964627754694</v>
+        <v>2871.533708172126</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2870.860314363086</v>
+        <v>2875.617276819583</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>2868.964362994341</v>
+        <v>2869.794016677204</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>2871.993238753537</v>
+        <v>2868.276018557071</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>2871.351894440406</v>
+        <v>2871.351427911023</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>2874.749981394216</v>
+        <v>2868.965040039346</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>2869.543761846663</v>
+        <v>2869.047470678556</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>2871.200979536628</v>
+        <v>2868.885579727789</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>2871.112981883371</v>
+        <v>2871.351365300758</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>2870.860165419359</v>
+        <v>2868.184325389537</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>2868.96439310131</v>
+        <v>2868.54841725601</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>2874.393673962085</v>
+        <v>2871.567646696346</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>2875.966828463754</v>
+        <v>2870.715412686682</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>2869.316006030082</v>
+        <v>2871.625537364383</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>2871.566984494101</v>
+        <v>2869.030384820519</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>2868.190419093317</v>
+        <v>2868.557294622509</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>2868.618975503386</v>
+        <v>2868.284262551274</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>2869.03419588253</v>
+        <v>2868.188086260079</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>2869.041615160746</v>
+        <v>2870.859756421718</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>2871.351363840232</v>
+        <v>2868.971779639095</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>2771.900797700995</v>
+        <v>2868.99828193002</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>2868.370493170647</v>
+        <v>2868.433706703021</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>2868.964375814598</v>
+        <v>2868.40275895955</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>2868.972270365049</v>
+        <v>2870.68971869149</v>
       </c>
       <c r="AD14" s="8" t="n">
-        <v>2871.351366582862</v>
+        <v>2869.172187008212</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>2871.30795583522</v>
+        <v>2868.193092913665</v>
       </c>
       <c r="AF14" s="14">
         <f>AVERAGE(B14:AE14)</f>

--- a/CoDPSO_Results_D10.xlsx
+++ b/CoDPSO_Results_D10.xlsx
@@ -617,22 +617,22 @@
         <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>341.2767252782094</v>
+        <v>342.4559034081973</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>24.26519444520479</v>
+        <v>33.74724686291918</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>301.9143542803455</v>
+        <v>308.1056691682635</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>395.9127863568975</v>
+        <v>426.0311641747334</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>41.27672527820937</v>
+        <v>42.45590340819734</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>24.26519444520479</v>
+        <v>33.74724686291918</v>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
@@ -654,22 +654,22 @@
         <v>1.95</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>409.0570042477048</v>
+        <v>406.0021229741299</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>5.782418012014913</v>
+        <v>4.618539930216754</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>401.5352477151633</v>
+        <v>400.3754187012455</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>430.018465005009</v>
+        <v>419.6591666146508</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>8.277004247704781</v>
+        <v>5.222122974129888</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>3.832418012014913</v>
+        <v>2.668539930216753</v>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
@@ -691,22 +691,22 @@
         <v>0.00898</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>600.0005312746379</v>
+        <v>600.0003707931495</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.0002265240092068909</v>
+        <v>0.0001780915900060968</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>600.0001507317784</v>
+        <v>600.0000976350716</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>600.0010791176591</v>
+        <v>600.0007611323484</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.0005312746378649535</v>
+        <v>0.0003707931495000594</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.008753475990793109</v>
+        <v>-0.008801908409993904</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -728,22 +728,22 @@
         <v>2.67</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>831.0972777942225</v>
+        <v>831.1077837065531</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>11.2789593674607</v>
+        <v>10.41631858375625</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>816.0001941859394</v>
+        <v>810.7187046434451</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>852.0000007805262</v>
+        <v>850.0047364939478</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>24.26727779422242</v>
+        <v>24.27778370655301</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>8.608959367460701</v>
+        <v>7.746318583756254</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
         <v>0.0413</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>900.1481647637037</v>
+        <v>900.1757090823718</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1388866884074056</v>
+        <v>0.1714785592915913</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>900.0040942381161</v>
+        <v>900.0035227624228</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>900.5494548576048</v>
+        <v>900.6282739396792</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.1381647637036849</v>
+        <v>0.1657090823717908</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.09758668840740564</v>
+        <v>0.1301785592915913</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -802,22 +802,22 @@
         <v>59.1</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>17481.39541177408</v>
+        <v>20442.78864452233</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>6048.262535437532</v>
+        <v>7175.926753649466</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>5025.937928620318</v>
+        <v>6526.750530161829</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>29691.02286936876</v>
+        <v>34572.69394470188</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>15609.53541177408</v>
+        <v>18570.92864452233</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5989.162535437532</v>
+        <v>7116.826753649466</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -839,22 +839,22 @@
         <v>9.66</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2040.475195562317</v>
+        <v>2038.988281713023</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8.124199473454231</v>
+        <v>6.864376840847735</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2021.013690010596</v>
+        <v>2028.201668014731</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2061.463757656976</v>
+        <v>2061.866485083521</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>31.12519556231723</v>
+        <v>29.63828171302316</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.535800526545769</v>
+        <v>-2.795623159152265</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -876,22 +876,22 @@
         <v>10</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2260.669409745225</v>
+        <v>2262.259269747914</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>49.3529727926692</v>
+        <v>40.50584483420965</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2227.597503796951</v>
+        <v>2229.71199389678</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2500.679190173065</v>
+        <v>2406.665740950526</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>50.60940974522509</v>
+        <v>52.19926974791406</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>39.3529727926692</v>
+        <v>30.50584483420965</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -913,22 +913,22 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2482.559203627215</v>
+        <v>2440.863954265734</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>174.95896824201</v>
+        <v>164.6393236727111</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2304.368804120033</v>
+        <v>2303.563432011429</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2736.444970119394</v>
+        <v>2679.479579700304</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>-46.72079637278557</v>
+        <v>-88.41604573426639</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>174.95896824201</v>
+        <v>164.6393236727111</v>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
@@ -950,22 +950,22 @@
         <v>0.518</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2632.894283480912</v>
+        <v>2634.431004312083</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>22.30649103243176</v>
+        <v>28.15236060950486</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2623.414907756083</v>
+        <v>2621.754203747572</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2751.466995099225</v>
+        <v>2749.042320767114</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>132.2542834809124</v>
+        <v>133.7910043120828</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>21.78849103243176</v>
+        <v>27.63436060950486</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
         <v>54.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2606.053673131233</v>
+        <v>2604.451747050315</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.777740123804923</v>
+        <v>4.134436089743791</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2601.319994148277</v>
+        <v>2601.186842779634</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2622.66273382562</v>
+        <v>2622.376810103934</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>-3.946326868767301</v>
+        <v>-5.54825294968532</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-49.02225987619507</v>
+        <v>-50.6655639102562</v>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
@@ -1024,22 +1024,22 @@
         <v>0.946</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2869.939433637538</v>
+        <v>2870.09893381996</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>1.764276732667429</v>
+        <v>1.398170449365345</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2868.184325389537</v>
+        <v>2868.193288163057</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2875.617276819583</v>
+        <v>2874.669751477849</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>8.329433637537932</v>
+        <v>8.488933819959584</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.8182767326674287</v>
+        <v>0.4521704493653451</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -1901,94 +1901,94 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>321.9124517871341</v>
+        <v>326.3392650830181</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>314.0707706730805</v>
+        <v>316.728565193415</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>350.0046465464358</v>
+        <v>310.0742797109717</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>387.6400744134166</v>
+        <v>358.9244721998124</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>349.4792534340656</v>
+        <v>315.8537776608086</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>377.357365048929</v>
+        <v>337.5765775839828</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>335.492709703153</v>
+        <v>406.8716802951973</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>356.5127508918586</v>
+        <v>343.946877435724</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>359.9154739430958</v>
+        <v>311.1014181365412</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>395.9127863568975</v>
+        <v>332.3261761790072</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>306.4037853189984</v>
+        <v>426.0311641747334</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>334.5964368811302</v>
+        <v>317.5099189177711</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>365.7323947964663</v>
+        <v>321.0203697409431</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>310.7393124716679</v>
+        <v>322.5987760456102</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>327.8594050707321</v>
+        <v>325.7804630613491</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>328.2871226103289</v>
+        <v>320.9033687924036</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>321.8613859955478</v>
+        <v>339.0764987093278</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>301.9143542803455</v>
+        <v>327.2092708928911</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>378.80270963656</v>
+        <v>334.3353465934416</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>361.3371552250873</v>
+        <v>312.8722290654094</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>339.7957685245354</v>
+        <v>412.966906241114</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>346.1438792299954</v>
+        <v>316.9519514959995</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>334.1105529094777</v>
+        <v>393.8237941672078</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>325.7085015390989</v>
+        <v>366.0073006142983</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>341.8135047662314</v>
+        <v>401.3938095772205</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>325.5062287793513</v>
+        <v>327.4211217368962</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>334.1674940176969</v>
+        <v>326.9590941760356</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>305.3264138781733</v>
+        <v>331.5976249776272</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>335.5112668655145</v>
+        <v>308.1056691682635</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>364.3858027512757</v>
+        <v>381.3693346188967</v>
       </c>
       <c r="AF3" s="14">
         <f>AVERAGE(B3:AE3)</f>
@@ -2014,94 +2014,94 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>403.1020682528393</v>
+        <v>400.6326806828473</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>403.4935190084236</v>
+        <v>400.7186296137806</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>404.3846572609367</v>
+        <v>406.7799405021461</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>411.0016587795204</v>
+        <v>400.3754187012455</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>408.9793218372212</v>
+        <v>408.5786642041007</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>408.4232321419059</v>
+        <v>413.2391133647133</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>408.428281558807</v>
+        <v>404.9733710484788</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>404.2699469317884</v>
+        <v>404.4969878856677</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>408.5305076320592</v>
+        <v>402.0532728744332</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>412.0643131244716</v>
+        <v>409.4131020609529</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>412.7342574897095</v>
+        <v>404.1773723969777</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>404.3749917848873</v>
+        <v>401.9087285839899</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>411.279611662619</v>
+        <v>407.6743796613079</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>401.5352477151633</v>
+        <v>409.3318962888534</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>410.8458255261779</v>
+        <v>400.9567565523135</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>403.9600059869433</v>
+        <v>401.5295107268012</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>420.2550846258457</v>
+        <v>403.9864758203457</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>402.2936990990556</v>
+        <v>419.6591666146508</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>409.7057290122679</v>
+        <v>411.9101659523793</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>417.2920028116228</v>
+        <v>413.0391313251166</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>406.3927719348927</v>
+        <v>404.084165811793</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>412.198280839651</v>
+        <v>410.5462989992776</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>408.3116853445874</v>
+        <v>401.8757926412156</v>
       </c>
       <c r="Y4" s="8" t="n">
-        <v>407.563077246152</v>
+        <v>401.4957190679858</v>
       </c>
       <c r="Z4" s="8" t="n">
-        <v>411.2149046119302</v>
+        <v>405.3802948694362</v>
       </c>
       <c r="AA4" s="8" t="n">
-        <v>408.2752948529218</v>
+        <v>409.0834023535169</v>
       </c>
       <c r="AB4" s="8" t="n">
-        <v>407.8748188845341</v>
+        <v>408.5124248262783</v>
       </c>
       <c r="AC4" s="8" t="n">
-        <v>410.5247655293452</v>
+        <v>408.442299591805</v>
       </c>
       <c r="AD4" s="8" t="n">
-        <v>402.3821009398529</v>
+        <v>402.7265721737834</v>
       </c>
       <c r="AE4" s="8" t="n">
-        <v>430.018465005009</v>
+        <v>402.4819540277022</v>
       </c>
       <c r="AF4" s="14">
         <f>AVERAGE(B4:AE4)</f>
@@ -2127,94 +2127,94 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>600.000694450291</v>
+        <v>600.0005087059966</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>600.0001531142539</v>
+        <v>600.0004930312159</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>600.0008690321421</v>
+        <v>600.000397509963</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>600.0004471279427</v>
+        <v>600.0002829274508</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>600.0006846658384</v>
+        <v>600.0004644575605</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>600.0010791176591</v>
+        <v>600.0006531331085</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>600.0001943147299</v>
+        <v>600.0001234534652</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>600.0005062337818</v>
+        <v>600.0007611323484</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>600.0001507317784</v>
+        <v>600.0003796110598</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>600.0005434748451</v>
+        <v>600.0002466259327</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>600.0004629770082</v>
+        <v>600.0000976350716</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>600.000169718492</v>
+        <v>600.0004952877961</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>600.000444947748</v>
+        <v>600.0002306169525</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>600.0005040808539</v>
+        <v>600.0005713632312</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>600.0007384728082</v>
+        <v>600.0005674311367</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>600.000275426056</v>
+        <v>600.000221976649</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>600.0006960794104</v>
+        <v>600.00027159232</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>600.0006191650599</v>
+        <v>600.0005437161257</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>600.0005311717495</v>
+        <v>600.0002551406949</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>600.0007405632351</v>
+        <v>600.0004158571768</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>600.0004115172968</v>
+        <v>600.0002585311107</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>600.0004369921165</v>
+        <v>600.0001798680638</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>600.0003061778413</v>
+        <v>600.000144735081</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>600.0006594507098</v>
+        <v>600.0005594233336</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>600.0004385795211</v>
+        <v>600.0001538928677</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>600.0006465219577</v>
+        <v>600.000704697999</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>600.0005239484223</v>
+        <v>600.000291388014</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>600.0005656669412</v>
+        <v>600.0002460232911</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>600.0009949900953</v>
+        <v>600.0003044252202</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>600.0004495285518</v>
+        <v>600.0002996042481</v>
       </c>
       <c r="AF5" s="14">
         <f>AVERAGE(B5:AE5)</f>
@@ -2240,94 +2240,94 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>822.0016219140912</v>
+        <v>826.0000282340494</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>818.0000015561309</v>
+        <v>850.0047364939478</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>824.0005695965789</v>
+        <v>840.0049179559404</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>820.015101789144</v>
+        <v>836.0002499781705</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>830.0000013438486</v>
+        <v>815.6756758116799</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>818.0000002894594</v>
+        <v>844.5349172890362</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>828.0021762243275</v>
+        <v>838.0010173180951</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>816.0415363262896</v>
+        <v>836.0003380138306</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>830.008141243644</v>
+        <v>824.0087811585023</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>850.0000014890418</v>
+        <v>820.0051202774393</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>828.0012179909211</v>
+        <v>816.0000021818737</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>834.0000371136103</v>
+        <v>824.04445973513</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>824.048127898555</v>
+        <v>838.016171864236</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>830.0610070319133</v>
+        <v>826.0043306251143</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>832.0003021843006</v>
+        <v>830.0249587501911</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>820.1633055402108</v>
+        <v>836.0004279998345</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>842.0401415776919</v>
+        <v>818.0021286997518</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>846.0000000140686</v>
+        <v>832</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>830.9770806355097</v>
+        <v>844.000104435763</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>819.6910400244891</v>
+        <v>846.0000342162259</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>852.000000424985</v>
+        <v>841.1156210087256</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>828.4130799487483</v>
+        <v>810.7187046434451</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>816.0001941859394</v>
+        <v>824.0001768911478</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>832.0061586138727</v>
+        <v>812.0000631253706</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>844.0184232078475</v>
+        <v>836.183903967367</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>850.0000541855777</v>
+        <v>844.2512461934538</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>852.0000007805262</v>
+        <v>826.0000697223854</v>
       </c>
       <c r="AC6" s="8" t="n">
-        <v>821.3407927035115</v>
+        <v>832.0022602989494</v>
       </c>
       <c r="AD6" s="8" t="n">
-        <v>828.0882179918352</v>
+        <v>834.0001021802719</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>846.0000000000058</v>
+        <v>832.6329621266644</v>
       </c>
       <c r="AF6" s="14">
         <f>AVERAGE(B6:AE6)</f>
@@ -2353,94 +2353,94 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>900.2119505884526</v>
+        <v>900.1050063303301</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>900.1587795703563</v>
+        <v>900.0103140205509</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>900.0137780937523</v>
+        <v>900.0529736027349</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>900.493637923997</v>
+        <v>900.0951286302311</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>900.0704908080892</v>
+        <v>900.0975543703846</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>900.2844683377039</v>
+        <v>900.1030661826325</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>900.2075477895318</v>
+        <v>900.1900333812841</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>900.0928669627586</v>
+        <v>900.5599841672125</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>900.0226336782196</v>
+        <v>900.0906734995167</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>900.0140605986109</v>
+        <v>900.1824876047342</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>900.1111722845966</v>
+        <v>900.4904593456737</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>900.1027580705271</v>
+        <v>900.4893477430528</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>900.0085653124434</v>
+        <v>900.0969943663058</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>900.5494548576048</v>
+        <v>900.0181448979204</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>900.010479045329</v>
+        <v>900.0129744486468</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>900.0462144792057</v>
+        <v>900.025239124079</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>900.2233463542666</v>
+        <v>900.6282739396792</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>900.1350553521734</v>
+        <v>900.4579424685384</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>900.0343474543939</v>
+        <v>900.0985818421988</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>900.0040942381161</v>
+        <v>900.0924269931209</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>900.1864908091544</v>
+        <v>900.0812002322585</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>900.0195301761563</v>
+        <v>900.264359427968</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>900.161829560605</v>
+        <v>900.0041833216482</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>900.4327683389189</v>
+        <v>900.1577531163742</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>900.1857645542412</v>
+        <v>900.2245193020584</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>900.1235467522696</v>
+        <v>900.1806348454215</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>900.1015054269752</v>
+        <v>900.2186079616138</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>900.0438645444419</v>
+        <v>900.0035227624228</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>900.1852354494749</v>
+        <v>900.1187706518123</v>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>900.2087054987505</v>
+        <v>900.120113890746</v>
       </c>
       <c r="AF7" s="14">
         <f>AVERAGE(B7:AE7)</f>
@@ -2466,94 +2466,94 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>20641.59216537873</v>
+        <v>15630.51175219357</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>22578.49338522329</v>
+        <v>16734.60129208741</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>10862.20832302194</v>
+        <v>27535.33258295625</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>18168.30260875679</v>
+        <v>23346.13178332412</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>16232.84726293689</v>
+        <v>29425.22815070977</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>9411.654045410703</v>
+        <v>25280.90393479783</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>17003.3321624544</v>
+        <v>8773.75088060403</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5025.937928620318</v>
+        <v>10643.60309518329</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>20641.18429682944</v>
+        <v>28458.35634606663</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>15637.68643934662</v>
+        <v>13874.95116891531</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>19760.89149975024</v>
+        <v>34572.69394470188</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>12342.70237424351</v>
+        <v>31999.7945603621</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>23903.0801485195</v>
+        <v>27032.32077633831</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>20799.33293960076</v>
+        <v>18441.94718119699</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>17085.46576967182</v>
+        <v>21064.69491332384</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>20383.0840708264</v>
+        <v>17107.53966565456</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>13078.04438130791</v>
+        <v>24298.49636007976</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>8144.488528078272</v>
+        <v>19209.85686320477</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>12672.27608863283</v>
+        <v>6526.750530161829</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>8750.981268674008</v>
+        <v>9167.257498621229</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>28503.55649558385</v>
+        <v>21268.0891291456</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>17554.05617494225</v>
+        <v>18283.29036384292</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>28131.29917345991</v>
+        <v>31869.77084822909</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>17763.75503129092</v>
+        <v>12850.18109899384</v>
       </c>
       <c r="Z8" s="8" t="n">
-        <v>9465.404666185932</v>
+        <v>21215.9920453924</v>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>21286.50622260097</v>
+        <v>18454.97174113079</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>21230.13928527885</v>
+        <v>13734.14348585075</v>
       </c>
       <c r="AC8" s="8" t="n">
-        <v>20037.61224116832</v>
+        <v>18926.32876628086</v>
       </c>
       <c r="AD8" s="8" t="n">
-        <v>29691.02286936876</v>
+        <v>25839.80104451408</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>17654.92450605825</v>
+        <v>21716.36753180612</v>
       </c>
       <c r="AF8" s="14">
         <f>AVERAGE(B8:AE8)</f>
@@ -2579,94 +2579,94 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2044.455452800737</v>
+        <v>2036.602797117512</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2056.106296537024</v>
+        <v>2029.645144513951</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2038.035013907244</v>
+        <v>2030.7740747464</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2040.472808779659</v>
+        <v>2037.281138460068</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2043.853492872288</v>
+        <v>2036.79220454497</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2037.171005495361</v>
+        <v>2045.120794683829</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2048.757664399437</v>
+        <v>2039.763730582484</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2030.644569298526</v>
+        <v>2036.290352462536</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2040.42400891951</v>
+        <v>2046.082815561119</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2034.674710421522</v>
+        <v>2048.455079356819</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2042.219449894825</v>
+        <v>2040.20334317127</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2044.141362350047</v>
+        <v>2040.329073729194</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2034.55375258638</v>
+        <v>2036.92314541319</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2044.676517661042</v>
+        <v>2032.438725196385</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2038.143388566359</v>
+        <v>2034.637565219311</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2039.723696986222</v>
+        <v>2045.138446393818</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2031.939891828064</v>
+        <v>2040.458956394936</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>2031.274257299484</v>
+        <v>2037.35548944657</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>2035.621612912873</v>
+        <v>2035.153117120781</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2051.598816910738</v>
+        <v>2035.999164241405</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2044.004459812047</v>
+        <v>2036.399346726863</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2040.207807908164</v>
+        <v>2039.327999909621</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2040.332267915169</v>
+        <v>2054.20164737161</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2039.399041097204</v>
+        <v>2028.201668014731</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2021.013690010596</v>
+        <v>2061.866485083521</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>2033.525804087</v>
+        <v>2035.058878645266</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>2061.463757656976</v>
+        <v>2040.795001617438</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>2035.311821958664</v>
+        <v>2037.335375392163</v>
       </c>
       <c r="AD9" s="4" t="n">
-        <v>2036.335298467357</v>
+        <v>2036.061027407175</v>
       </c>
       <c r="AE9" s="4" t="n">
-        <v>2054.174147529007</v>
+        <v>2034.955862865764</v>
       </c>
       <c r="AF9" s="14">
         <f>AVERAGE(B9:AE9)</f>
@@ -2692,94 +2692,94 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>2245.290346552693</v>
+        <v>2277.600694072931</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2237.39428418271</v>
+        <v>2232.769375639581</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2276.552244503348</v>
+        <v>2377.943435686149</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>2244.247178077148</v>
+        <v>2234.161731953539</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2271.937376079521</v>
+        <v>2406.665740950526</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2229.800575824169</v>
+        <v>2280.699462039537</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>2236.314067256545</v>
+        <v>2235.017094508957</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>2244.485689705265</v>
+        <v>2236.900371069283</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>2227.597503796951</v>
+        <v>2266.125495087429</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>2270.803184844114</v>
+        <v>2264.01361443109</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>2242.365362463114</v>
+        <v>2241.449037876778</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>2228.984267355373</v>
+        <v>2243.027831238639</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>2242.144302970354</v>
+        <v>2229.71199389678</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>2231.825393349728</v>
+        <v>2237.375550407278</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>2302.461712666685</v>
+        <v>2320.883495525314</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>2258.18810197484</v>
+        <v>2262.077185580884</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>2258.764591552238</v>
+        <v>2236.600491488858</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>2234.203262914444</v>
+        <v>2268.750490137769</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>2282.421151575762</v>
+        <v>2232.716730915766</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>2261.891643996481</v>
+        <v>2237.533740006662</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>2237.655354644296</v>
+        <v>2248.336888212493</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>2241.10976669832</v>
+        <v>2233.028147401458</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>2243.2315484926</v>
+        <v>2242.036522338257</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>2239.346817170516</v>
+        <v>2262.088477781303</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>2500.679190173065</v>
+        <v>2281.202239113646</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>2315.762208817869</v>
+        <v>2262.295681475794</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>2238.562241243082</v>
+        <v>2239.801721432802</v>
       </c>
       <c r="AC10" s="8" t="n">
-        <v>2271.528821549473</v>
+        <v>2255.173570413651</v>
       </c>
       <c r="AD10" s="8" t="n">
-        <v>2260.499548553656</v>
+        <v>2281.759596007613</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>2244.034553372376</v>
+        <v>2240.031685746664</v>
       </c>
       <c r="AF10" s="14">
         <f>AVERAGE(B10:AE10)</f>
@@ -2805,94 +2805,94 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2356.839794868658</v>
+        <v>2421.529014212632</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2736.444970119394</v>
+        <v>2325.006094309125</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2670.136108532151</v>
+        <v>2303.563432011429</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2318.290410915088</v>
+        <v>2305.569852585906</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2675.26743251075</v>
+        <v>2333.621067229651</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2309.003033828419</v>
+        <v>2310.571067401675</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2670.672230181071</v>
+        <v>2310.408245040956</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2366.556335944204</v>
+        <v>2670.218270018609</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2310.184435241171</v>
+        <v>2670.124166531387</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2667.000015288601</v>
+        <v>2670.121874243679</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2667.958764001588</v>
+        <v>2317.718278674497</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2668.868952503279</v>
+        <v>2316.222531107896</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2676.338006307773</v>
+        <v>2329.595848612</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2680.251216736825</v>
+        <v>2372.495848979034</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2312.574703193933</v>
+        <v>2663.339637027891</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2307.277266833745</v>
+        <v>2304.920501449129</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2328.079020666872</v>
+        <v>2312.725119104709</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2307.878952581268</v>
+        <v>2672.254259239125</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2667.372549255771</v>
+        <v>2671.260107581061</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2305.953281398236</v>
+        <v>2679.479579700304</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2320.601204773012</v>
+        <v>2666.209155293664</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2670.121343943819</v>
+        <v>2376.014127750268</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2313.341767635307</v>
+        <v>2677.930762176873</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>2675.656567617533</v>
+        <v>2311.032555871823</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2309.421687799866</v>
+        <v>2312.291464852039</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>2308.895088722029</v>
+        <v>2671.015541299913</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>2680.271324810987</v>
+        <v>2316.386442246941</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>2304.368804120033</v>
+        <v>2312.44548354574</v>
       </c>
       <c r="AD11" s="4" t="n">
-        <v>2516.113225118315</v>
+        <v>2311.774848106082</v>
       </c>
       <c r="AE11" s="4" t="n">
-        <v>2375.037613366744</v>
+        <v>2310.073451767964</v>
       </c>
       <c r="AF11" s="14">
         <f>AVERAGE(B11:AE11)</f>
@@ -2918,94 +2918,94 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>2624.112055992699</v>
+        <v>2636.242598754007</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>2630.103106368782</v>
+        <v>2626.477461022348</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2629.884121646029</v>
+        <v>2625.115256841839</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2628.155256210339</v>
+        <v>2624.707945599587</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2625.514147540115</v>
+        <v>2624.109796016043</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2627.91941492664</v>
+        <v>2627.639360862649</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>2625.941452122996</v>
+        <v>2623.418271396964</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>2625.316417320637</v>
+        <v>2627.58871908217</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>2633.918827405399</v>
+        <v>2627.606952661581</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>2630.707881185127</v>
+        <v>2627.566284800228</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>2628.612866757715</v>
+        <v>2624.045103907323</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>2634.443459010084</v>
+        <v>2622.971123001714</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>2636.872104968443</v>
+        <v>2749.042320767114</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>2635.935133002065</v>
+        <v>2628.131007845033</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>2628.903410288913</v>
+        <v>2627.186475072508</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>2635.082854883137</v>
+        <v>2624.181865711728</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>2623.414907756083</v>
+        <v>2624.658891829475</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>2628.870877428848</v>
+        <v>2625.338511654023</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>2631.747948591898</v>
+        <v>2633.948783647262</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>2626.412942086477</v>
+        <v>2621.754203747572</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>2629.681435653506</v>
+        <v>2628.174727686519</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>2627.949111180134</v>
+        <v>2621.940752615831</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>2624.798708861438</v>
+        <v>2622.303465716727</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>2630.277897383314</v>
+        <v>2627.621000475719</v>
       </c>
       <c r="Z12" s="8" t="n">
-        <v>2623.779567792526</v>
+        <v>2727.640116453728</v>
       </c>
       <c r="AA12" s="8" t="n">
-        <v>2626.605150267518</v>
+        <v>2627.655585375993</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>2751.466995099225</v>
+        <v>2633.468044014743</v>
       </c>
       <c r="AC12" s="8" t="n">
-        <v>2628.30622102076</v>
+        <v>2633.010687768853</v>
       </c>
       <c r="AD12" s="8" t="n">
-        <v>2626.324294325309</v>
+        <v>2625.643356420557</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>2625.769937351196</v>
+        <v>2633.741458612632</v>
       </c>
       <c r="AF12" s="14">
         <f>AVERAGE(B12:AE12)</f>
@@ -3031,94 +3031,94 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2601.566296411168</v>
+        <v>2604.162091108988</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2604.225326361059</v>
+        <v>2601.573802039557</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2602.157395048499</v>
+        <v>2605.157240725941</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2602.634505984717</v>
+        <v>2603.785929559257</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2616.492279450525</v>
+        <v>2604.814016686266</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2602.919870502931</v>
+        <v>2601.772557971682</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2603.469473132985</v>
+        <v>2601.881247545259</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2618.033208566118</v>
+        <v>2612.398127958415</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2602.43866456828</v>
+        <v>2608.078885148319</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2605.879094134668</v>
+        <v>2602.118257842053</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2610.606772880424</v>
+        <v>2604.767270066475</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2602.320763314845</v>
+        <v>2603.641831914885</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2602.938688156172</v>
+        <v>2601.535546643885</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2606.842049761417</v>
+        <v>2608.940570553673</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2603.964216140795</v>
+        <v>2602.988742871388</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2601.464571282288</v>
+        <v>2603.155570256164</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>2604.47396301658</v>
+        <v>2602.952730491409</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>2603.814982526348</v>
+        <v>2601.186842779634</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>2604.215190851144</v>
+        <v>2601.287609630328</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2622.66273382562</v>
+        <v>2603.429681839944</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2601.319994148277</v>
+        <v>2601.214385162518</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2605.890774758822</v>
+        <v>2604.919369141536</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2602.390553721258</v>
+        <v>2603.312860795758</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2604.610115345456</v>
+        <v>2603.238093618683</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2601.401367629295</v>
+        <v>2606.790982380988</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>2605.260168418212</v>
+        <v>2603.206237580044</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>2619.653576914802</v>
+        <v>2602.091310305495</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>2601.728297630881</v>
+        <v>2604.095321170712</v>
       </c>
       <c r="AD13" s="4" t="n">
-        <v>2603.674353305375</v>
+        <v>2622.376810103934</v>
       </c>
       <c r="AE13" s="4" t="n">
-        <v>2612.56094614802</v>
+        <v>2602.67848761626</v>
       </c>
       <c r="AF13" s="14">
         <f>AVERAGE(B13:AE13)</f>
@@ -3144,94 +3144,94 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>2873.675668038233</v>
+        <v>2868.964332114836</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2871.49425486583</v>
+        <v>2868.375752309141</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2870.730595407148</v>
+        <v>2868.679509135804</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>2869.037937017383</v>
+        <v>2871.122276201673</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2871.533708172126</v>
+        <v>2868.970158805238</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2875.617276819583</v>
+        <v>2871.567279324547</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>2869.794016677204</v>
+        <v>2870.352669373041</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>2868.276018557071</v>
+        <v>2870.776720546078</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>2871.351427911023</v>
+        <v>2871.351363496346</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>2868.965040039346</v>
+        <v>2868.965801275318</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>2869.047470678556</v>
+        <v>2871.100890541713</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>2868.885579727789</v>
+        <v>2868.193288163057</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>2871.351365300758</v>
+        <v>2870.782285181968</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>2868.184325389537</v>
+        <v>2871.351931434438</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>2868.54841725601</v>
+        <v>2868.966522013549</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>2871.567646696346</v>
+        <v>2868.983245258134</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>2870.715412686682</v>
+        <v>2869.012969694706</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>2871.625537364383</v>
+        <v>2868.422150224265</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>2869.030384820519</v>
+        <v>2869.14421152381</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>2868.557294622509</v>
+        <v>2871.119579791233</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>2868.284262551274</v>
+        <v>2870.022798409936</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>2868.188086260079</v>
+        <v>2870.777836832156</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>2870.859756421718</v>
+        <v>2869.722398401373</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>2868.971779639095</v>
+        <v>2868.97759548474</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>2868.99828193002</v>
+        <v>2869.202367804729</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>2868.433706703021</v>
+        <v>2871.3513863892</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>2868.40275895955</v>
+        <v>2871.56707960648</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>2870.68971869149</v>
+        <v>2871.250178403812</v>
       </c>
       <c r="AD14" s="8" t="n">
-        <v>2869.172187008212</v>
+        <v>2874.669751477849</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>2868.193092913665</v>
+        <v>2869.223685379623</v>
       </c>
       <c r="AF14" s="14">
         <f>AVERAGE(B14:AE14)</f>

--- a/CoDPSO_Results_D10.xlsx
+++ b/CoDPSO_Results_D10.xlsx
@@ -617,22 +617,22 @@
         <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>342.4559034081973</v>
+        <v>361.5255277923499</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>33.74724686291918</v>
+        <v>41.6609673843808</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>308.1056691682635</v>
+        <v>303.4071813107659</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>426.0311641747334</v>
+        <v>465.4884479344549</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>42.45590340819734</v>
+        <v>61.52552779234986</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>33.74724686291918</v>
+        <v>41.6609673843808</v>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
@@ -654,22 +654,22 @@
         <v>1.95</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>406.0021229741299</v>
+        <v>407.1635731501261</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>4.618539930216754</v>
+        <v>4.479138863721167</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>400.3754187012455</v>
+        <v>400.8240422783372</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>419.6591666146508</v>
+        <v>423.0206071114724</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>5.222122974129888</v>
+        <v>6.383573150126097</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>2.668539930216753</v>
+        <v>2.529138863721167</v>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
@@ -691,22 +691,22 @@
         <v>0.00898</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>600.0003707931495</v>
+        <v>600.0005327860814</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.0001780915900060968</v>
+        <v>0.0003526088408974042</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>600.0000976350716</v>
+        <v>600.0000992154812</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>600.0007611323484</v>
+        <v>600.0014778646824</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.0003707931495000594</v>
+        <v>0.0005327860814077212</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.008801908409993904</v>
+        <v>-0.008627391159102596</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -728,22 +728,22 @@
         <v>2.67</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>831.1077837065531</v>
+        <v>829.8408631219298</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>10.41631858375625</v>
+        <v>8.673879352661286</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>810.7187046434451</v>
+        <v>814.576713536744</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>850.0047364939478</v>
+        <v>844.0002146522356</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>24.27778370655301</v>
+        <v>23.01086312192979</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>7.746318583756254</v>
+        <v>6.003879352661286</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
         <v>0.0413</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>900.1757090823718</v>
+        <v>900.2419161681593</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1714785592915913</v>
+        <v>0.2117464303597375</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>900.0035227624228</v>
+        <v>900.0095341146111</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>900.6282739396792</v>
+        <v>900.916660203855</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.1657090823717908</v>
+        <v>0.2319161681592732</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1301785592915913</v>
+        <v>0.1704464303597375</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -802,22 +802,22 @@
         <v>59.1</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>20442.78864452233</v>
+        <v>15945.8256141365</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>7175.926753649466</v>
+        <v>6211.920411766658</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>6526.750530161829</v>
+        <v>5433.228342735481</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>34572.69394470188</v>
+        <v>29511.92460572807</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>18570.92864452233</v>
+        <v>14073.9656141365</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>7116.826753649466</v>
+        <v>6152.820411766657</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -839,22 +839,22 @@
         <v>9.66</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2038.988281713023</v>
+        <v>2040.625400263491</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.864376840847735</v>
+        <v>8.028467366967361</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2028.201668014731</v>
+        <v>2026.055861615045</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2061.866485083521</v>
+        <v>2055.263419620967</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>29.63828171302316</v>
+        <v>31.27540026349129</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.795623159152265</v>
+        <v>-1.63153263303264</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -876,22 +876,22 @@
         <v>10</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2262.259269747914</v>
+        <v>2265.985427854587</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>40.50584483420965</v>
+        <v>33.08799443658943</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2229.71199389678</v>
+        <v>2232.54831023024</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2406.665740950526</v>
+        <v>2364.277944859386</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>52.19926974791406</v>
+        <v>55.92542785458681</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>30.50584483420965</v>
+        <v>23.08799443658943</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -913,22 +913,22 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2440.863954265734</v>
+        <v>2458.226850064216</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>164.6393236727111</v>
+        <v>166.299446673084</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2303.563432011429</v>
+        <v>2302.871047487976</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2679.479579700304</v>
+        <v>2685.635044175283</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>-88.41604573426639</v>
+        <v>-71.05314993578395</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>164.6393236727111</v>
+        <v>166.299446673084</v>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
@@ -950,22 +950,22 @@
         <v>0.518</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2634.431004312083</v>
+        <v>2631.663303077698</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>28.15236060950486</v>
+        <v>19.92927519039115</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2621.754203747572</v>
+        <v>2621.912955919088</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2749.042320767114</v>
+        <v>2737.461861643262</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>133.7910043120828</v>
+        <v>131.0233030776981</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>27.63436060950486</v>
+        <v>19.41127519039115</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
         <v>54.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2604.451747050315</v>
+        <v>2603.094973576014</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.134436089743791</v>
+        <v>2.251111717319487</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2601.186842779634</v>
+        <v>2601.199086919918</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2622.376810103934</v>
+        <v>2613.465606203702</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>-5.54825294968532</v>
+        <v>-6.905026423986328</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-50.6655639102562</v>
+        <v>-52.54888828268051</v>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
@@ -1024,22 +1024,22 @@
         <v>0.946</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2870.09893381996</v>
+        <v>2869.534379364793</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>1.398170449365345</v>
+        <v>1.386944785891577</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2868.193288163057</v>
+        <v>2866.483286660208</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2874.669751477849</v>
+        <v>2871.642573487779</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>8.488933819959584</v>
+        <v>7.924379364792458</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.4521704493653451</v>
+        <v>0.4409447858915769</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -1901,94 +1901,94 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>326.3392650830181</v>
+        <v>420.9908092402636</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>316.728565193415</v>
+        <v>454.1209925992216</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>310.0742797109717</v>
+        <v>376.3683527813702</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>358.9244721998124</v>
+        <v>303.4071813107659</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>315.8537776608086</v>
+        <v>356.7045432332897</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>337.5765775839828</v>
+        <v>404.8690847612032</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>406.8716802951973</v>
+        <v>335.4459784075326</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>343.946877435724</v>
+        <v>320.6580074379457</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>311.1014181365412</v>
+        <v>378.3363060027584</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>332.3261761790072</v>
+        <v>382.6611910744388</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>426.0311641747334</v>
+        <v>408.5613119862915</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>317.5099189177711</v>
+        <v>401.0196793244363</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>321.0203697409431</v>
+        <v>320.1030995564457</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>322.5987760456102</v>
+        <v>379.1234345647153</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>325.7804630613491</v>
+        <v>327.4549615621276</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>320.9033687924036</v>
+        <v>322.975950283474</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>339.0764987093278</v>
+        <v>396.9934102281561</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>327.2092708928911</v>
+        <v>397.3442077239271</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>334.3353465934416</v>
+        <v>322.0500004733734</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>312.8722290654094</v>
+        <v>331.4872086427741</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>412.966906241114</v>
+        <v>360.657127956658</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>316.9519514959995</v>
+        <v>323.0150987035598</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>393.8237941672078</v>
+        <v>334.6380248339022</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>366.0073006142983</v>
+        <v>324.6306182263328</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>401.3938095772205</v>
+        <v>351.6220763118131</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>327.4211217368962</v>
+        <v>323.0333724195868</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>326.9590941760356</v>
+        <v>360.639514694384</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>331.5976249776272</v>
+        <v>336.768398871633</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>308.1056691682635</v>
+        <v>465.4884479344549</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>381.3693346188967</v>
+        <v>324.5974426236618</v>
       </c>
       <c r="AF3" s="14">
         <f>AVERAGE(B3:AE3)</f>
@@ -2014,94 +2014,94 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>400.6326806828473</v>
+        <v>402.7684966000693</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>400.7186296137806</v>
+        <v>403.3327294920668</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>406.7799405021461</v>
+        <v>411.3511088557756</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>400.3754187012455</v>
+        <v>406.5059577232565</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>408.5786642041007</v>
+        <v>400.8240422783372</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>413.2391133647133</v>
+        <v>408.3657278372455</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>404.9733710484788</v>
+        <v>407.0632577175348</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>404.4969878856677</v>
+        <v>403.8775267393817</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>402.0532728744332</v>
+        <v>408.8765201177171</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>409.4131020609529</v>
+        <v>407.3450049310541</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>404.1773723969777</v>
+        <v>407.2987862636901</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>401.9087285839899</v>
+        <v>410.8220207421629</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>407.6743796613079</v>
+        <v>411.2716749951225</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>409.3318962888534</v>
+        <v>409.2339298897122</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>400.9567565523135</v>
+        <v>402.78272509934</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>401.5295107268012</v>
+        <v>402.5357054675363</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>403.9864758203457</v>
+        <v>410.3918860588995</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>419.6591666146508</v>
+        <v>409.5839513258777</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>411.9101659523793</v>
+        <v>410.5884488780297</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>413.0391313251166</v>
+        <v>401.4758646123083</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>404.084165811793</v>
+        <v>406.2362790091232</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>410.5462989992776</v>
+        <v>409.6700535812371</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>401.8757926412156</v>
+        <v>410.8789323585264</v>
       </c>
       <c r="Y4" s="8" t="n">
-        <v>401.4957190679858</v>
+        <v>402.9907521246309</v>
       </c>
       <c r="Z4" s="8" t="n">
-        <v>405.3802948694362</v>
+        <v>401.4556190535251</v>
       </c>
       <c r="AA4" s="8" t="n">
-        <v>409.0834023535169</v>
+        <v>403.1861604328385</v>
       </c>
       <c r="AB4" s="8" t="n">
-        <v>408.5124248262783</v>
+        <v>403.6919388672537</v>
       </c>
       <c r="AC4" s="8" t="n">
-        <v>408.442299591805</v>
+        <v>410.1089814291578</v>
       </c>
       <c r="AD4" s="8" t="n">
-        <v>402.7265721737834</v>
+        <v>407.3725049108983</v>
       </c>
       <c r="AE4" s="8" t="n">
-        <v>402.4819540277022</v>
+        <v>423.0206071114724</v>
       </c>
       <c r="AF4" s="14">
         <f>AVERAGE(B4:AE4)</f>
@@ -2127,94 +2127,94 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>600.0005087059966</v>
+        <v>600.0013788170503</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>600.0004930312159</v>
+        <v>600.0002759992343</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>600.000397509963</v>
+        <v>600.0002956388056</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>600.0002829274508</v>
+        <v>600.0005340325159</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>600.0004644575605</v>
+        <v>600.0003306472061</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>600.0006531331085</v>
+        <v>600.0014778646824</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>600.0001234534652</v>
+        <v>600.0003445402141</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>600.0007611323484</v>
+        <v>600.0005265995748</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>600.0003796110598</v>
+        <v>600.0008503437019</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>600.0002466259327</v>
+        <v>600.0009594456276</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>600.0000976350716</v>
+        <v>600.0005375892654</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>600.0004952877961</v>
+        <v>600.000234478868</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>600.0002306169525</v>
+        <v>600.000233470666</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>600.0005713632312</v>
+        <v>600.0001575176098</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>600.0005674311367</v>
+        <v>600.0013132009612</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>600.000221976649</v>
+        <v>600.0000992154812</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>600.00027159232</v>
+        <v>600.0004958291033</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>600.0005437161257</v>
+        <v>600.000198938789</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>600.0002551406949</v>
+        <v>600.0002017780362</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>600.0004158571768</v>
+        <v>600.0004265025474</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>600.0002585311107</v>
+        <v>600.0003199449268</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>600.0001798680638</v>
+        <v>600.0002683284192</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>600.000144735081</v>
+        <v>600.0003198936598</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>600.0005594233336</v>
+        <v>600.000733284353</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>600.0001538928677</v>
+        <v>600.0004764486445</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>600.000704697999</v>
+        <v>600.0006244554218</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>600.000291388014</v>
+        <v>600.0006413013316</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>600.0002460232911</v>
+        <v>600.000730550202</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>600.0003044252202</v>
+        <v>600.0003890763593</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>600.0002996042481</v>
+        <v>600.0006078491846</v>
       </c>
       <c r="AF5" s="14">
         <f>AVERAGE(B5:AE5)</f>
@@ -2240,94 +2240,94 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>826.0000282340494</v>
+        <v>816.0029478878902</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>850.0047364939478</v>
+        <v>836.0075863035028</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>840.0049179559404</v>
+        <v>836.0079811465753</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>836.0002499781705</v>
+        <v>834.4325388452221</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>815.6756758116799</v>
+        <v>838.0006586651903</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>844.5349172890362</v>
+        <v>838.0312118244892</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>838.0010173180951</v>
+        <v>840.0051353223214</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>836.0003380138306</v>
+        <v>840.0002313360019</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>824.0087811585023</v>
+        <v>820.0002621433032</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>820.0051202774393</v>
+        <v>825.2309235670307</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>816.0000021818737</v>
+        <v>828.000013416948</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>824.04445973513</v>
+        <v>818.4390375342094</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>838.016171864236</v>
+        <v>823.1985174474312</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>826.0043306251143</v>
+        <v>844.0000135899032</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>830.0249587501911</v>
+        <v>820.0121093532653</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>836.0004279998345</v>
+        <v>830.016543242516</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>818.0021286997518</v>
+        <v>824.0000003344646</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>832</v>
+        <v>826.0016948406562</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>844.000104435763</v>
+        <v>844.0002146522356</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>846.0000342162259</v>
+        <v>830.0033613899026</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>841.1156210087256</v>
+        <v>834.7728894610322</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>810.7187046434451</v>
+        <v>826.1130194264462</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>824.0001768911478</v>
+        <v>840.0066383821966</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>812.0000631253706</v>
+        <v>822.0000029032416</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>836.183903967367</v>
+        <v>814.576713536744</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>844.2512461934538</v>
+        <v>832.813349809114</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>826.0000697223854</v>
+        <v>833.4800914817139</v>
       </c>
       <c r="AC6" s="8" t="n">
-        <v>832.0022602989494</v>
+        <v>816.0000335121691</v>
       </c>
       <c r="AD6" s="8" t="n">
-        <v>834.0001021802719</v>
+        <v>824.0720002860303</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>832.6329621266644</v>
+        <v>840.0001720161486</v>
       </c>
       <c r="AF6" s="14">
         <f>AVERAGE(B6:AE6)</f>
@@ -2353,94 +2353,94 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>900.1050063303301</v>
+        <v>900.103073040422</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>900.0103140205509</v>
+        <v>900.916660203855</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>900.0529736027349</v>
+        <v>900.1247857770868</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>900.0951286302311</v>
+        <v>900.1065792052111</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>900.0975543703846</v>
+        <v>900.182725814533</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>900.1030661826325</v>
+        <v>900.3241140807201</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>900.1900333812841</v>
+        <v>900.093052858267</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>900.5599841672125</v>
+        <v>900.1102287955664</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>900.0906734995167</v>
+        <v>900.4552053822622</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>900.1824876047342</v>
+        <v>900.1097741971154</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>900.4904593456737</v>
+        <v>900.1370666824632</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>900.4893477430528</v>
+        <v>900.0973136737143</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>900.0969943663058</v>
+        <v>900.1063873084341</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>900.0181448979204</v>
+        <v>900.5770784742201</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>900.0129744486468</v>
+        <v>900.0826460885953</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>900.025239124079</v>
+        <v>900.5584894417008</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>900.6282739396792</v>
+        <v>900.5252133598027</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>900.4579424685384</v>
+        <v>900.4229766747981</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>900.0985818421988</v>
+        <v>900.0095341146111</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>900.0924269931209</v>
+        <v>900.0211516511494</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>900.0812002322585</v>
+        <v>900.1067161622095</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>900.264359427968</v>
+        <v>900.1886585668434</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>900.0041833216482</v>
+        <v>900.6091323766791</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>900.1577531163742</v>
+        <v>900.1822501351462</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>900.2245193020584</v>
+        <v>900.1943158186094</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>900.1806348454215</v>
+        <v>900.2753645632519</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>900.2186079616138</v>
+        <v>900.0930415349804</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>900.0035227624228</v>
+        <v>900.1875344764301</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>900.1187706518123</v>
+        <v>900.064909983927</v>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>900.120113890746</v>
+        <v>900.2915046021762</v>
       </c>
       <c r="AF7" s="14">
         <f>AVERAGE(B7:AE7)</f>
@@ -2466,94 +2466,94 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>15630.51175219357</v>
+        <v>25298.74202856733</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>16734.60129208741</v>
+        <v>19121.63696116208</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>27535.33258295625</v>
+        <v>15178.66749906807</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>23346.13178332412</v>
+        <v>10734.79018907541</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>29425.22815070977</v>
+        <v>19605.03937390367</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>25280.90393479783</v>
+        <v>20826.44450655431</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>8773.75088060403</v>
+        <v>12670.70394967191</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>10643.60309518329</v>
+        <v>14588.60442383063</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>28458.35634606663</v>
+        <v>15185.38427654161</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>13874.95116891531</v>
+        <v>13136.32360367071</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>34572.69394470188</v>
+        <v>26091.79008430067</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>31999.7945603621</v>
+        <v>8681.249668900695</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>27032.32077633831</v>
+        <v>18197.78549980608</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>18441.94718119699</v>
+        <v>15371.59281487943</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>21064.69491332384</v>
+        <v>20518.96550296429</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>17107.53966565456</v>
+        <v>22348.97923630883</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>24298.49636007976</v>
+        <v>12179.79881353355</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>19209.85686320477</v>
+        <v>16591.10553614695</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>6526.750530161829</v>
+        <v>29511.92460572807</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>9167.257498621229</v>
+        <v>5433.228342735481</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>21268.0891291456</v>
+        <v>6566.946631789148</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>18283.29036384292</v>
+        <v>5997.236547392213</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>31869.77084822909</v>
+        <v>20330.83825643284</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>12850.18109899384</v>
+        <v>9134.64737295176</v>
       </c>
       <c r="Z8" s="8" t="n">
-        <v>21215.9920453924</v>
+        <v>13670.6711540964</v>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>18454.97174113079</v>
+        <v>10922.67185098809</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>13734.14348585075</v>
+        <v>21931.57539691891</v>
       </c>
       <c r="AC8" s="8" t="n">
-        <v>18926.32876628086</v>
+        <v>10442.85681493113</v>
       </c>
       <c r="AD8" s="8" t="n">
-        <v>25839.80104451408</v>
+        <v>12989.25761045158</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>21716.36753180612</v>
+        <v>25115.30987079328</v>
       </c>
       <c r="AF8" s="14">
         <f>AVERAGE(B8:AE8)</f>
@@ -2579,94 +2579,94 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2036.602797117512</v>
+        <v>2045.888725998574</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2029.645144513951</v>
+        <v>2031.103165050863</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2030.7740747464</v>
+        <v>2028.894369296055</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2037.281138460068</v>
+        <v>2047.333837053807</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2036.79220454497</v>
+        <v>2047.659621146345</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2045.120794683829</v>
+        <v>2038.029694166643</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2039.763730582484</v>
+        <v>2038.170690403951</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2036.290352462536</v>
+        <v>2028.740040807533</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2046.082815561119</v>
+        <v>2038.180925702935</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2048.455079356819</v>
+        <v>2049.808260383828</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2040.20334317127</v>
+        <v>2047.256560251627</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2040.329073729194</v>
+        <v>2026.510521086622</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2036.92314541319</v>
+        <v>2040.456388764997</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2032.438725196385</v>
+        <v>2031.10980145001</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2034.637565219311</v>
+        <v>2034.634454236838</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2045.138446393818</v>
+        <v>2042.799152904652</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2040.458956394936</v>
+        <v>2035.220061692831</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>2037.35548944657</v>
+        <v>2055.263419620967</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>2035.153117120781</v>
+        <v>2048.025732817275</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2035.999164241405</v>
+        <v>2053.690878266543</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2036.399346726863</v>
+        <v>2048.872711547389</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2039.327999909621</v>
+        <v>2046.455189346791</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2054.20164737161</v>
+        <v>2043.324352569</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2028.201668014731</v>
+        <v>2043.348996868815</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2061.866485083521</v>
+        <v>2030.313971969019</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>2035.058878645266</v>
+        <v>2043.671658236005</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>2040.795001617438</v>
+        <v>2047.686510390961</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>2037.335375392163</v>
+        <v>2026.055861615045</v>
       </c>
       <c r="AD9" s="4" t="n">
-        <v>2036.061027407175</v>
+        <v>2040.673700673946</v>
       </c>
       <c r="AE9" s="4" t="n">
-        <v>2034.955862865764</v>
+        <v>2039.582753584868</v>
       </c>
       <c r="AF9" s="14">
         <f>AVERAGE(B9:AE9)</f>
@@ -2692,94 +2692,94 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>2277.600694072931</v>
+        <v>2283.896633639951</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2232.769375639581</v>
+        <v>2258.429973834677</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2377.943435686149</v>
+        <v>2259.695976962278</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>2234.161731953539</v>
+        <v>2239.461570010761</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2406.665740950526</v>
+        <v>2267.605599210583</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2280.699462039537</v>
+        <v>2252.634875439434</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>2235.017094508957</v>
+        <v>2282.586861190676</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>2236.900371069283</v>
+        <v>2293.039990328679</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>2266.125495087429</v>
+        <v>2232.54831023024</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>2264.01361443109</v>
+        <v>2235.754519536971</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>2241.449037876778</v>
+        <v>2364.277944859386</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>2243.027831238639</v>
+        <v>2253.941045457138</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>2229.71199389678</v>
+        <v>2273.66122264841</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>2237.375550407278</v>
+        <v>2270.142154981856</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>2320.883495525314</v>
+        <v>2247.290694458624</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>2262.077185580884</v>
+        <v>2242.963287733893</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>2236.600491488858</v>
+        <v>2236.072730484763</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>2268.750490137769</v>
+        <v>2232.659586094473</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>2232.716730915766</v>
+        <v>2299.913420007302</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>2237.533740006662</v>
+        <v>2258.715547609696</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>2248.336888212493</v>
+        <v>2363.773034862572</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>2233.028147401458</v>
+        <v>2242.135812097011</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>2242.036522338257</v>
+        <v>2248.20120626069</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>2262.088477781303</v>
+        <v>2274.261342145646</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>2281.202239113646</v>
+        <v>2236.814186890071</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>2262.295681475794</v>
+        <v>2287.17789394186</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>2239.801721432802</v>
+        <v>2301.506617275185</v>
       </c>
       <c r="AC10" s="8" t="n">
-        <v>2255.173570413651</v>
+        <v>2244.897405512221</v>
       </c>
       <c r="AD10" s="8" t="n">
-        <v>2281.759596007613</v>
+        <v>2260.868875792101</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>2240.031685746664</v>
+        <v>2234.634516140445</v>
       </c>
       <c r="AF10" s="14">
         <f>AVERAGE(B10:AE10)</f>
@@ -2805,94 +2805,94 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2421.529014212632</v>
+        <v>2318.698841834612</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2325.006094309125</v>
+        <v>2305.887139457918</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2303.563432011429</v>
+        <v>2672.208207978722</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2305.569852585906</v>
+        <v>2307.490023213351</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2333.621067229651</v>
+        <v>2685.635044175283</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2310.571067401675</v>
+        <v>2671.608335922674</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2310.408245040956</v>
+        <v>2665.753172222281</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2670.218270018609</v>
+        <v>2674.559808925224</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2670.124166531387</v>
+        <v>2672.343005903517</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2670.121874243679</v>
+        <v>2327.481202897155</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2317.718278674497</v>
+        <v>2670.27877757808</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2316.222531107896</v>
+        <v>2421.797476596912</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2329.595848612</v>
+        <v>2302.871047487976</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2372.495848979034</v>
+        <v>2409.350139281543</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2663.339637027891</v>
+        <v>2411.121194395843</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2304.920501449129</v>
+        <v>2305.536865688045</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2312.725119104709</v>
+        <v>2334.25484550512</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2672.254259239125</v>
+        <v>2681.640539667023</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2671.260107581061</v>
+        <v>2359.349435695414</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2679.479579700304</v>
+        <v>2319.874873711154</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2666.209155293664</v>
+        <v>2317.415292728092</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2376.014127750268</v>
+        <v>2305.038936251933</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2677.930762176873</v>
+        <v>2310.727902101934</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>2311.032555871823</v>
+        <v>2316.132023140364</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2312.291464852039</v>
+        <v>2667.747856662822</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>2671.015541299913</v>
+        <v>2322.398190164991</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>2316.386442246941</v>
+        <v>2326.823043542389</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>2312.44548354574</v>
+        <v>2672.317966665526</v>
       </c>
       <c r="AD11" s="4" t="n">
-        <v>2311.774848106082</v>
+        <v>2671.930704606089</v>
       </c>
       <c r="AE11" s="4" t="n">
-        <v>2310.073451767964</v>
+        <v>2318.533607924516</v>
       </c>
       <c r="AF11" s="14">
         <f>AVERAGE(B11:AE11)</f>
@@ -2918,94 +2918,94 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>2636.242598754007</v>
+        <v>2625.839377303151</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>2626.477461022348</v>
+        <v>2629.010688572572</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2625.115256841839</v>
+        <v>2625.839276584403</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2624.707945599587</v>
+        <v>2632.180399576212</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2624.109796016043</v>
+        <v>2626.402067183656</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2627.639360862649</v>
+        <v>2737.461861643262</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>2623.418271396964</v>
+        <v>2630.996465722446</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>2627.58871908217</v>
+        <v>2628.901532541812</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>2627.606952661581</v>
+        <v>2634.483952592561</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>2627.566284800228</v>
+        <v>2627.272133900254</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>2624.045103907323</v>
+        <v>2628.449906614619</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>2622.971123001714</v>
+        <v>2630.177721742218</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>2749.042320767114</v>
+        <v>2625.127641988157</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>2628.131007845033</v>
+        <v>2631.07025577392</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>2627.186475072508</v>
+        <v>2623.53382738762</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>2624.181865711728</v>
+        <v>2628.195324481413</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>2624.658891829475</v>
+        <v>2623.397645309722</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>2625.338511654023</v>
+        <v>2635.280541765062</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>2633.948783647262</v>
+        <v>2628.654844921918</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>2621.754203747572</v>
+        <v>2634.372607368021</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>2628.174727686519</v>
+        <v>2631.050084965285</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>2621.940752615831</v>
+        <v>2624.425300277951</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>2622.303465716727</v>
+        <v>2627.555390842258</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>2627.621000475719</v>
+        <v>2627.856231510575</v>
       </c>
       <c r="Z12" s="8" t="n">
-        <v>2727.640116453728</v>
+        <v>2625.841875216235</v>
       </c>
       <c r="AA12" s="8" t="n">
-        <v>2627.655585375993</v>
+        <v>2621.912955919088</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>2633.468044014743</v>
+        <v>2626.308454694314</v>
       </c>
       <c r="AC12" s="8" t="n">
-        <v>2633.010687768853</v>
+        <v>2628.947654450276</v>
       </c>
       <c r="AD12" s="8" t="n">
-        <v>2625.643356420557</v>
+        <v>2626.339511163158</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>2633.741458612632</v>
+        <v>2623.0135603188</v>
       </c>
       <c r="AF12" s="14">
         <f>AVERAGE(B12:AE12)</f>
@@ -3031,94 +3031,94 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2604.162091108988</v>
+        <v>2604.647729136572</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2601.573802039557</v>
+        <v>2602.201621309162</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2605.157240725941</v>
+        <v>2613.465606203702</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2603.785929559257</v>
+        <v>2601.579168598673</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2604.814016686266</v>
+        <v>2603.512920107592</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2601.772557971682</v>
+        <v>2601.92736003792</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2601.881247545259</v>
+        <v>2604.234153926723</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2612.398127958415</v>
+        <v>2602.399703249465</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2608.078885148319</v>
+        <v>2602.270115951309</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2602.118257842053</v>
+        <v>2603.493745892476</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2604.767270066475</v>
+        <v>2601.815926763052</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2603.641831914885</v>
+        <v>2603.147824949659</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2601.535546643885</v>
+        <v>2602.726278405997</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2608.940570553673</v>
+        <v>2602.255836092423</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2602.988742871388</v>
+        <v>2602.818496703191</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2603.155570256164</v>
+        <v>2601.288679680151</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>2602.952730491409</v>
+        <v>2602.563463329616</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>2601.186842779634</v>
+        <v>2602.360824332865</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>2601.287609630328</v>
+        <v>2601.921094243339</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2603.429681839944</v>
+        <v>2601.199086919918</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2601.214385162518</v>
+        <v>2601.900123894163</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2604.919369141536</v>
+        <v>2602.37238206398</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2603.312860795758</v>
+        <v>2602.594252302787</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2603.238093618683</v>
+        <v>2602.162079417319</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2606.790982380988</v>
+        <v>2605.462670575364</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>2603.206237580044</v>
+        <v>2603.436705862912</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>2602.091310305495</v>
+        <v>2602.93919696585</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>2604.095321170712</v>
+        <v>2601.73810793314</v>
       </c>
       <c r="AD13" s="4" t="n">
-        <v>2622.376810103934</v>
+        <v>2606.450423813315</v>
       </c>
       <c r="AE13" s="4" t="n">
-        <v>2602.67848761626</v>
+        <v>2601.963628617792</v>
       </c>
       <c r="AF13" s="14">
         <f>AVERAGE(B13:AE13)</f>
@@ -3144,94 +3144,94 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>2868.964332114836</v>
+        <v>2869.999982707491</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2868.375752309141</v>
+        <v>2868.990438867067</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2868.679509135804</v>
+        <v>2868.739160756363</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>2871.122276201673</v>
+        <v>2870.734017179998</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2868.970158805238</v>
+        <v>2871.287601259388</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2871.567279324547</v>
+        <v>2868.143057043623</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>2870.352669373041</v>
+        <v>2869.720557239706</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>2870.776720546078</v>
+        <v>2869.029717878817</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>2871.351363496346</v>
+        <v>2868.964296278296</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>2868.965801275318</v>
+        <v>2868.580526213833</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>2871.100890541713</v>
+        <v>2869.030845284196</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>2868.193288163057</v>
+        <v>2871.642573487779</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>2870.782285181968</v>
+        <v>2869.376062935909</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>2871.351931434438</v>
+        <v>2871.351357263054</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>2868.966522013549</v>
+        <v>2871.569709361844</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>2868.983245258134</v>
+        <v>2868.955090150477</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>2869.012969694706</v>
+        <v>2868.081853085628</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>2868.422150224265</v>
+        <v>2871.351606032794</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>2869.14421152381</v>
+        <v>2871.177684909105</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>2871.119579791233</v>
+        <v>2869.007085234019</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>2870.022798409936</v>
+        <v>2870.775450636919</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>2870.777836832156</v>
+        <v>2868.48737835962</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>2869.722398401373</v>
+        <v>2871.351697434598</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>2868.97759548474</v>
+        <v>2871.559404910815</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>2869.202367804729</v>
+        <v>2867.579574221299</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>2871.3513863892</v>
+        <v>2868.274288564655</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>2871.56707960648</v>
+        <v>2869.037450153248</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>2871.250178403812</v>
+        <v>2868.335676212138</v>
       </c>
       <c r="AD14" s="8" t="n">
-        <v>2874.669751477849</v>
+        <v>2866.483286660208</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>2869.223685379623</v>
+        <v>2868.413950620889</v>
       </c>
       <c r="AF14" s="14">
         <f>AVERAGE(B14:AE14)</f>
